--- a/sample_data/5月小红书投放.xlsx
+++ b/sample_data/5月小红书投放.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K301"/>
+  <dimension ref="A1:M301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,6 +472,16 @@
           <t>录入日期</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>消耗</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>活动名</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -479,10 +489,8 @@
           <t>何洋</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>13607963731</t>
-        </is>
+      <c r="B2" t="n">
+        <v>13607963731</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -527,6 +535,14 @@
           <t>2024-03-02</t>
         </is>
       </c>
+      <c r="L2" t="n">
+        <v>203</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -534,10 +550,8 @@
           <t>吴艳涛</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>13984523542</t>
-        </is>
+      <c r="B3" t="n">
+        <v>13984523542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -578,6 +592,14 @@
           <t>2024-04-09</t>
         </is>
       </c>
+      <c r="L3" t="n">
+        <v>506.2</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -585,10 +607,8 @@
           <t>褚平刚</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>13886523777</t>
-        </is>
+      <c r="B4" t="n">
+        <v>13886523777</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
@@ -629,6 +649,14 @@
           <t>2024-02-27</t>
         </is>
       </c>
+      <c r="L4" t="n">
+        <v>689.64</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -636,10 +664,8 @@
           <t>秦芳芳</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>13652781055</t>
-        </is>
+      <c r="B5" t="n">
+        <v>13652781055</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -684,6 +710,14 @@
           <t>2024-04-05</t>
         </is>
       </c>
+      <c r="L5" t="n">
+        <v>89.16</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -691,10 +725,8 @@
           <t>何涛强</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>13960943913</t>
-        </is>
+      <c r="B6" t="n">
+        <v>13960943913</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -731,6 +763,14 @@
           <t>2024-04-11</t>
         </is>
       </c>
+      <c r="L6" t="n">
+        <v>460.06</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -738,10 +778,8 @@
           <t>孔霞</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>13528620929</t>
-        </is>
+      <c r="B7" t="n">
+        <v>13528620929</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -782,6 +820,14 @@
           <t>2024-12-15</t>
         </is>
       </c>
+      <c r="L7" t="n">
+        <v>499.7</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -789,10 +835,8 @@
           <t>沈磊</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>15073938992</t>
-        </is>
+      <c r="B8" t="n">
+        <v>15073938992</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
@@ -833,6 +877,14 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="L8" t="n">
+        <v>329.88</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -840,10 +892,8 @@
           <t>华娜芳</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>18661087082</t>
-        </is>
+      <c r="B9" t="n">
+        <v>18661087082</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -888,6 +938,14 @@
           <t>2024-09-08</t>
         </is>
       </c>
+      <c r="L9" t="n">
+        <v>454.31</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -895,10 +953,8 @@
           <t>王静</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>15883882176</t>
-        </is>
+      <c r="B10" t="n">
+        <v>15883882176</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -939,6 +995,14 @@
           <t>2024-03-08</t>
         </is>
       </c>
+      <c r="L10" t="n">
+        <v>443.21</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -946,10 +1010,8 @@
           <t>陈强强</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>13522280194</t>
-        </is>
+      <c r="B11" t="n">
+        <v>13522280194</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
@@ -990,6 +1052,14 @@
           <t>2024-06-30</t>
         </is>
       </c>
+      <c r="L11" t="n">
+        <v>178.73</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -997,10 +1067,8 @@
           <t>曹芳</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>13795350637</t>
-        </is>
+      <c r="B12" t="n">
+        <v>13795350637</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1041,6 +1109,14 @@
           <t>2024-04-30</t>
         </is>
       </c>
+      <c r="L12" t="n">
+        <v>84.48</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1048,10 +1124,8 @@
           <t>赵明磊</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>13784185201</t>
-        </is>
+      <c r="B13" t="n">
+        <v>13784185201</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
@@ -1088,6 +1162,14 @@
           <t>2024-04-27</t>
         </is>
       </c>
+      <c r="L13" t="n">
+        <v>739.42</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1095,10 +1177,8 @@
           <t>陶刚</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>13954705549</t>
-        </is>
+      <c r="B14" t="n">
+        <v>13954705549</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
@@ -1135,6 +1215,14 @@
           <t>2024-10-16</t>
         </is>
       </c>
+      <c r="L14" t="n">
+        <v>528.88</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1142,10 +1230,8 @@
           <t>吕勇</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>13891969395</t>
-        </is>
+      <c r="B15" t="n">
+        <v>13891969395</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1186,6 +1272,14 @@
           <t>2024-03-27</t>
         </is>
       </c>
+      <c r="L15" t="n">
+        <v>56.36</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1193,10 +1287,8 @@
           <t>华丽娜</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>18871212413</t>
-        </is>
+      <c r="B16" t="n">
+        <v>18871212413</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1237,6 +1329,14 @@
           <t>2024-09-24</t>
         </is>
       </c>
+      <c r="L16" t="n">
+        <v>459.41</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1244,10 +1344,8 @@
           <t>陶强</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>15977319227</t>
-        </is>
+      <c r="B17" t="n">
+        <v>15977319227</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1292,6 +1390,14 @@
           <t>2024-08-03</t>
         </is>
       </c>
+      <c r="L17" t="n">
+        <v>171.23</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1299,10 +1405,8 @@
           <t>施磊强</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>18994319165</t>
-        </is>
+      <c r="B18" t="n">
+        <v>18994319165</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1339,6 +1443,14 @@
           <t>2024-03-02</t>
         </is>
       </c>
+      <c r="L18" t="n">
+        <v>217.47</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1346,10 +1458,8 @@
           <t>周艳文</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>15876449747</t>
-        </is>
+      <c r="B19" t="n">
+        <v>15876449747</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
@@ -1386,6 +1496,14 @@
           <t>2024-06-07</t>
         </is>
       </c>
+      <c r="L19" t="n">
+        <v>248.5</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1393,10 +1511,8 @@
           <t>华明</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>18879741636</t>
-        </is>
+      <c r="B20" t="n">
+        <v>18879741636</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1441,6 +1557,14 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="L20" t="n">
+        <v>51.23</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1448,10 +1572,8 @@
           <t>韩明</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>18864969277</t>
-        </is>
+      <c r="B21" t="n">
+        <v>18864969277</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
@@ -1484,6 +1606,14 @@
           <t>2024-01-26</t>
         </is>
       </c>
+      <c r="L21" t="n">
+        <v>451.96</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1491,10 +1621,8 @@
           <t>张兰</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>13825512827</t>
-        </is>
+      <c r="B22" t="n">
+        <v>13825512827</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1539,6 +1667,14 @@
           <t>2024-06-27</t>
         </is>
       </c>
+      <c r="L22" t="n">
+        <v>106.47</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1546,10 +1682,8 @@
           <t>尤娟磊</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>15254434414</t>
-        </is>
+      <c r="B23" t="n">
+        <v>15254434414</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1590,6 +1724,14 @@
           <t>2024-05-25</t>
         </is>
       </c>
+      <c r="L23" t="n">
+        <v>492.76</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1597,10 +1739,8 @@
           <t>韩兰娟</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>15208822309</t>
-        </is>
+      <c r="B24" t="n">
+        <v>15208822309</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1641,6 +1781,14 @@
           <t>2024-03-21</t>
         </is>
       </c>
+      <c r="L24" t="n">
+        <v>523.86</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1648,10 +1796,8 @@
           <t>郑伟文</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>18872021707</t>
-        </is>
+      <c r="B25" t="n">
+        <v>18872021707</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1692,6 +1838,14 @@
           <t>2024-10-26</t>
         </is>
       </c>
+      <c r="L25" t="n">
+        <v>399.13</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1699,10 +1853,8 @@
           <t>冯文</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>15100449646</t>
-        </is>
+      <c r="B26" t="n">
+        <v>15100449646</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1743,6 +1895,14 @@
           <t>2024-02-28</t>
         </is>
       </c>
+      <c r="L26" t="n">
+        <v>675.78</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1750,10 +1910,8 @@
           <t>沈英勇</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>13765896359</t>
-        </is>
+      <c r="B27" t="n">
+        <v>13765896359</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1798,6 +1956,14 @@
           <t>2024-12-27</t>
         </is>
       </c>
+      <c r="L27" t="n">
+        <v>732.45</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1805,10 +1971,8 @@
           <t>张秀</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>15256631138</t>
-        </is>
+      <c r="B28" t="n">
+        <v>15256631138</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1853,6 +2017,14 @@
           <t>2024-03-10</t>
         </is>
       </c>
+      <c r="L28" t="n">
+        <v>56.31</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1860,10 +2032,8 @@
           <t>孙磊</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>18642463104</t>
-        </is>
+      <c r="B29" t="n">
+        <v>18642463104</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
@@ -1904,6 +2074,14 @@
           <t>2024-11-29</t>
         </is>
       </c>
+      <c r="L29" t="n">
+        <v>564.73</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1911,10 +2089,8 @@
           <t>何桂静</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>18846902177</t>
-        </is>
+      <c r="B30" t="n">
+        <v>18846902177</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1959,6 +2135,14 @@
           <t>2024-04-26</t>
         </is>
       </c>
+      <c r="L30" t="n">
+        <v>533.55</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1966,10 +2150,8 @@
           <t>张芳</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>13789466527</t>
-        </is>
+      <c r="B31" t="n">
+        <v>13789466527</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -2010,6 +2192,14 @@
           <t>2024-01-05</t>
         </is>
       </c>
+      <c r="L31" t="n">
+        <v>662.03</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2017,10 +2207,8 @@
           <t>冯伟</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>15991330303</t>
-        </is>
+      <c r="B32" t="n">
+        <v>15991330303</v>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
@@ -2057,6 +2245,14 @@
           <t>2024-07-05</t>
         </is>
       </c>
+      <c r="L32" t="n">
+        <v>596.29</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2064,10 +2260,8 @@
           <t>赵涛静</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>13679955302</t>
-        </is>
+      <c r="B33" t="n">
+        <v>13679955302</v>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
@@ -2104,6 +2298,14 @@
           <t>2024-10-11</t>
         </is>
       </c>
+      <c r="L33" t="n">
+        <v>306.49</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2111,10 +2313,8 @@
           <t>朱明</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>13834202847</t>
-        </is>
+      <c r="B34" t="n">
+        <v>13834202847</v>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
@@ -2147,6 +2347,14 @@
           <t>2024-05-29</t>
         </is>
       </c>
+      <c r="L34" t="n">
+        <v>498.32</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2154,10 +2362,8 @@
           <t>李艳</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>13764871775</t>
-        </is>
+      <c r="B35" t="n">
+        <v>13764871775</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -2198,6 +2404,14 @@
           <t>2024-04-26</t>
         </is>
       </c>
+      <c r="L35" t="n">
+        <v>729.24</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2205,10 +2419,8 @@
           <t>金静明</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>18925812259</t>
-        </is>
+      <c r="B36" t="n">
+        <v>18925812259</v>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
@@ -2241,6 +2453,14 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="L36" t="n">
+        <v>643.74</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2248,10 +2468,8 @@
           <t>陈磊</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>18937912121</t>
-        </is>
+      <c r="B37" t="n">
+        <v>18937912121</v>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
@@ -2292,6 +2510,14 @@
           <t>2024-12-18</t>
         </is>
       </c>
+      <c r="L37" t="n">
+        <v>424.02</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2299,10 +2525,8 @@
           <t>严华霞</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>13817074039</t>
-        </is>
+      <c r="B38" t="n">
+        <v>13817074039</v>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
@@ -2343,6 +2567,14 @@
           <t>2024-03-29</t>
         </is>
       </c>
+      <c r="L38" t="n">
+        <v>452.58</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2350,10 +2582,8 @@
           <t>卫静杰</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>13543387220</t>
-        </is>
+      <c r="B39" t="n">
+        <v>13543387220</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -2394,6 +2624,14 @@
           <t>2024-10-29</t>
         </is>
       </c>
+      <c r="L39" t="n">
+        <v>518.85</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2401,10 +2639,8 @@
           <t>孔强英</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>13508334447</t>
-        </is>
+      <c r="B40" t="n">
+        <v>13508334447</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -2449,6 +2685,14 @@
           <t>2024-08-25</t>
         </is>
       </c>
+      <c r="L40" t="n">
+        <v>404.25</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2456,10 +2700,8 @@
           <t>钱华</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>13759685195</t>
-        </is>
+      <c r="B41" t="n">
+        <v>13759685195</v>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
@@ -2492,6 +2734,14 @@
           <t>2024-12-02</t>
         </is>
       </c>
+      <c r="L41" t="n">
+        <v>200.98</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2499,10 +2749,8 @@
           <t>沈丽霞</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>13556342777</t>
-        </is>
+      <c r="B42" t="n">
+        <v>13556342777</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -2543,6 +2791,14 @@
           <t>2024-02-12</t>
         </is>
       </c>
+      <c r="L42" t="n">
+        <v>787.79</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2550,10 +2806,8 @@
           <t>陈华伟</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>18959229411</t>
-        </is>
+      <c r="B43" t="n">
+        <v>18959229411</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -2594,6 +2848,14 @@
           <t>2024-12-24</t>
         </is>
       </c>
+      <c r="L43" t="n">
+        <v>701.42</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2601,10 +2863,8 @@
           <t>曹磊</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>18626294206</t>
-        </is>
+      <c r="B44" t="n">
+        <v>18626294206</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -2645,6 +2905,14 @@
           <t>2024-04-14</t>
         </is>
       </c>
+      <c r="L44" t="n">
+        <v>181.32</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2652,10 +2920,8 @@
           <t>郑磊文</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>13700498321</t>
-        </is>
+      <c r="B45" t="n">
+        <v>13700498321</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -2700,6 +2966,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="L45" t="n">
+        <v>547.8200000000001</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2707,10 +2981,8 @@
           <t>王桂</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>15068687640</t>
-        </is>
+      <c r="B46" t="n">
+        <v>15068687640</v>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
@@ -2747,6 +3019,14 @@
           <t>2024-06-05</t>
         </is>
       </c>
+      <c r="L46" t="n">
+        <v>70.95999999999999</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2754,10 +3034,8 @@
           <t>冯刚</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>13662987787</t>
-        </is>
+      <c r="B47" t="n">
+        <v>13662987787</v>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
@@ -2794,6 +3072,14 @@
           <t>2024-06-08</t>
         </is>
       </c>
+      <c r="L47" t="n">
+        <v>435.7</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2801,10 +3087,8 @@
           <t>王霞</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>15034219262</t>
-        </is>
+      <c r="B48" t="n">
+        <v>15034219262</v>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
@@ -2841,6 +3125,14 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="L48" t="n">
+        <v>740.02</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2848,10 +3140,8 @@
           <t>朱秀</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>13947891179</t>
-        </is>
+      <c r="B49" t="n">
+        <v>13947891179</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -2896,6 +3186,14 @@
           <t>2024-04-11</t>
         </is>
       </c>
+      <c r="L49" t="n">
+        <v>254.95</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2903,10 +3201,8 @@
           <t>王英芳</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>15166602000</t>
-        </is>
+      <c r="B50" t="n">
+        <v>15166602000</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -2947,6 +3243,14 @@
           <t>2024-01-02</t>
         </is>
       </c>
+      <c r="L50" t="n">
+        <v>657.35</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2954,10 +3258,8 @@
           <t>何平</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>13624383805</t>
-        </is>
+      <c r="B51" t="n">
+        <v>13624383805</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -3002,6 +3304,14 @@
           <t>2024-09-30</t>
         </is>
       </c>
+      <c r="L51" t="n">
+        <v>114.77</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3009,10 +3319,8 @@
           <t>华丽文</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>15933283896</t>
-        </is>
+      <c r="B52" t="n">
+        <v>15933283896</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -3057,6 +3365,14 @@
           <t>2024-11-19</t>
         </is>
       </c>
+      <c r="L52" t="n">
+        <v>632.59</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3064,10 +3380,8 @@
           <t>曹丽</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>13936841013</t>
-        </is>
+      <c r="B53" t="n">
+        <v>13936841013</v>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
@@ -3100,6 +3414,14 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="L53" t="n">
+        <v>534.47</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3107,10 +3429,8 @@
           <t>韩艳涛</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>13591875067</t>
-        </is>
+      <c r="B54" t="n">
+        <v>13591875067</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -3155,6 +3475,14 @@
           <t>2024-09-24</t>
         </is>
       </c>
+      <c r="L54" t="n">
+        <v>616.25</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3162,10 +3490,8 @@
           <t>郑平磊</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>13619279761</t>
-        </is>
+      <c r="B55" t="n">
+        <v>13619279761</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -3210,6 +3536,14 @@
           <t>2024-06-02</t>
         </is>
       </c>
+      <c r="L55" t="n">
+        <v>617.03</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3217,10 +3551,8 @@
           <t>施刚</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>13502665686</t>
-        </is>
+      <c r="B56" t="n">
+        <v>13502665686</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -3261,6 +3593,14 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="L56" t="n">
+        <v>721.3099999999999</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3268,10 +3608,8 @@
           <t>褚勇</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>18846074299</t>
-        </is>
+      <c r="B57" t="n">
+        <v>18846074299</v>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
@@ -3308,6 +3646,14 @@
           <t>2024-02-02</t>
         </is>
       </c>
+      <c r="L57" t="n">
+        <v>354.99</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3315,10 +3661,8 @@
           <t>金兰明</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>13880897474</t>
-        </is>
+      <c r="B58" t="n">
+        <v>13880897474</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -3355,6 +3699,14 @@
           <t>2024-09-15</t>
         </is>
       </c>
+      <c r="L58" t="n">
+        <v>694.49</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3362,10 +3714,8 @@
           <t>许敏</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>15147853698</t>
-        </is>
+      <c r="B59" t="n">
+        <v>15147853698</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -3406,6 +3756,14 @@
           <t>2024-03-26</t>
         </is>
       </c>
+      <c r="L59" t="n">
+        <v>583.91</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3413,10 +3771,8 @@
           <t>曹伟</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>15010262706</t>
-        </is>
+      <c r="B60" t="n">
+        <v>15010262706</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -3461,6 +3817,14 @@
           <t>2024-02-23</t>
         </is>
       </c>
+      <c r="L60" t="n">
+        <v>771.25</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3468,10 +3832,8 @@
           <t>韩伟秀</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>18883057488</t>
-        </is>
+      <c r="B61" t="n">
+        <v>18883057488</v>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
@@ -3504,6 +3866,14 @@
           <t>2024-01-08</t>
         </is>
       </c>
+      <c r="L61" t="n">
+        <v>132.13</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3511,10 +3881,8 @@
           <t>陈涛伟</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>13803056619</t>
-        </is>
+      <c r="B62" t="n">
+        <v>13803056619</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -3555,6 +3923,14 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="L62" t="n">
+        <v>71.56999999999999</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3562,10 +3938,8 @@
           <t>朱文涛</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>18746790870</t>
-        </is>
+      <c r="B63" t="n">
+        <v>18746790870</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -3610,6 +3984,14 @@
           <t>2024-08-06</t>
         </is>
       </c>
+      <c r="L63" t="n">
+        <v>152.4</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3617,10 +3999,8 @@
           <t>张桂</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>15144442990</t>
-        </is>
+      <c r="B64" t="n">
+        <v>15144442990</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -3665,6 +4045,14 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="L64" t="n">
+        <v>427.4</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3672,10 +4060,8 @@
           <t>陈华敏</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>15859967256</t>
-        </is>
+      <c r="B65" t="n">
+        <v>15859967256</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -3720,6 +4106,14 @@
           <t>2024-12-03</t>
         </is>
       </c>
+      <c r="L65" t="n">
+        <v>432.92</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3727,10 +4121,8 @@
           <t>尤涛军</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>18647648455</t>
-        </is>
+      <c r="B66" t="n">
+        <v>18647648455</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -3771,6 +4163,14 @@
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="L66" t="n">
+        <v>590.1799999999999</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3778,10 +4178,8 @@
           <t>吴静</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>13553129003</t>
-        </is>
+      <c r="B67" t="n">
+        <v>13553129003</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -3826,6 +4224,14 @@
           <t>2024-09-10</t>
         </is>
       </c>
+      <c r="L67" t="n">
+        <v>369.12</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3833,10 +4239,8 @@
           <t>褚娟秀</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>18983958558</t>
-        </is>
+      <c r="B68" t="n">
+        <v>18983958558</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -3873,6 +4277,14 @@
           <t>2024-02-21</t>
         </is>
       </c>
+      <c r="L68" t="n">
+        <v>220.31</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3880,10 +4292,8 @@
           <t>曹敏勇</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>18659171050</t>
-        </is>
+      <c r="B69" t="n">
+        <v>18659171050</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -3928,6 +4338,14 @@
           <t>2024-08-29</t>
         </is>
       </c>
+      <c r="L69" t="n">
+        <v>686.09</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3935,10 +4353,8 @@
           <t>韩文</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>15152478417</t>
-        </is>
+      <c r="B70" t="n">
+        <v>15152478417</v>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
@@ -3975,6 +4391,14 @@
           <t>2024-11-04</t>
         </is>
       </c>
+      <c r="L70" t="n">
+        <v>74.23999999999999</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3982,10 +4406,8 @@
           <t>沈芳</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>18688033183</t>
-        </is>
+      <c r="B71" t="n">
+        <v>18688033183</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -4026,6 +4448,14 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="L71" t="n">
+        <v>728.35</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4033,10 +4463,8 @@
           <t>陶超丽</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>13681527873</t>
-        </is>
+      <c r="B72" t="n">
+        <v>13681527873</v>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
@@ -4069,6 +4497,14 @@
           <t>2024-08-15</t>
         </is>
       </c>
+      <c r="L72" t="n">
+        <v>507.33</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4076,10 +4512,8 @@
           <t>许娟</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>18935378018</t>
-        </is>
+      <c r="B73" t="n">
+        <v>18935378018</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -4120,6 +4554,14 @@
           <t>2024-09-02</t>
         </is>
       </c>
+      <c r="L73" t="n">
+        <v>359.97</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4127,10 +4569,8 @@
           <t>金英</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>15096914336</t>
-        </is>
+      <c r="B74" t="n">
+        <v>15096914336</v>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr"/>
@@ -4167,6 +4607,14 @@
           <t>2024-10-27</t>
         </is>
       </c>
+      <c r="L74" t="n">
+        <v>452.19</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4174,10 +4622,8 @@
           <t>钱桂</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>13889857390</t>
-        </is>
+      <c r="B75" t="n">
+        <v>13889857390</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -4214,6 +4660,14 @@
           <t>2024-05-28</t>
         </is>
       </c>
+      <c r="L75" t="n">
+        <v>381.05</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4221,10 +4675,8 @@
           <t>尤丽杰</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>15288499795</t>
-        </is>
+      <c r="B76" t="n">
+        <v>15288499795</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -4265,6 +4717,14 @@
           <t>2024-02-26</t>
         </is>
       </c>
+      <c r="L76" t="n">
+        <v>774.34</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4272,10 +4732,8 @@
           <t>李丽</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>18697891248</t>
-        </is>
+      <c r="B77" t="n">
+        <v>18697891248</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -4316,6 +4774,14 @@
           <t>2024-02-20</t>
         </is>
       </c>
+      <c r="L77" t="n">
+        <v>642</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4323,10 +4789,8 @@
           <t>秦华娟</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>18628681123</t>
-        </is>
+      <c r="B78" t="n">
+        <v>18628681123</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -4367,6 +4831,14 @@
           <t>2024-11-08</t>
         </is>
       </c>
+      <c r="L78" t="n">
+        <v>764.3</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4374,10 +4846,8 @@
           <t>姜秀</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>15890099217</t>
-        </is>
+      <c r="B79" t="n">
+        <v>15890099217</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -4422,6 +4892,14 @@
           <t>2024-02-15</t>
         </is>
       </c>
+      <c r="L79" t="n">
+        <v>195.06</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4429,10 +4907,8 @@
           <t>何英文</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>13870532601</t>
-        </is>
+      <c r="B80" t="n">
+        <v>13870532601</v>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
@@ -4469,6 +4945,14 @@
           <t>2024-08-30</t>
         </is>
       </c>
+      <c r="L80" t="n">
+        <v>392.12</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4476,10 +4960,8 @@
           <t>许静勇</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>15813609085</t>
-        </is>
+      <c r="B81" t="n">
+        <v>15813609085</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -4516,6 +4998,14 @@
           <t>2024-04-18</t>
         </is>
       </c>
+      <c r="L81" t="n">
+        <v>747.5</v>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4523,10 +5013,8 @@
           <t>魏强</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>15887366271</t>
-        </is>
+      <c r="B82" t="n">
+        <v>15887366271</v>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
@@ -4567,6 +5055,14 @@
           <t>2024-11-12</t>
         </is>
       </c>
+      <c r="L82" t="n">
+        <v>205.35</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4574,10 +5070,8 @@
           <t>李桂</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>15885615473</t>
-        </is>
+      <c r="B83" t="n">
+        <v>15885615473</v>
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
@@ -4618,6 +5112,14 @@
           <t>2024-02-29</t>
         </is>
       </c>
+      <c r="L83" t="n">
+        <v>182.4</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4625,10 +5127,8 @@
           <t>郑杰</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>15990283772</t>
-        </is>
+      <c r="B84" t="n">
+        <v>15990283772</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -4669,6 +5169,14 @@
           <t>2024-05-31</t>
         </is>
       </c>
+      <c r="L84" t="n">
+        <v>89.19</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4676,10 +5184,8 @@
           <t>卫超</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>13644161019</t>
-        </is>
+      <c r="B85" t="n">
+        <v>13644161019</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -4716,6 +5222,14 @@
           <t>2024-01-22</t>
         </is>
       </c>
+      <c r="L85" t="n">
+        <v>143.71</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4723,10 +5237,8 @@
           <t>张敏</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>18988027304</t>
-        </is>
+      <c r="B86" t="n">
+        <v>18988027304</v>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
@@ -4763,6 +5275,14 @@
           <t>2024-05-12</t>
         </is>
       </c>
+      <c r="L86" t="n">
+        <v>593.17</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4770,10 +5290,8 @@
           <t>秦涛</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>13693953096</t>
-        </is>
+      <c r="B87" t="n">
+        <v>13693953096</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -4814,6 +5332,14 @@
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="L87" t="n">
+        <v>658.9</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4821,10 +5347,8 @@
           <t>秦霞文</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>15255135872</t>
-        </is>
+      <c r="B88" t="n">
+        <v>15255135872</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -4865,6 +5389,14 @@
           <t>2024-07-15</t>
         </is>
       </c>
+      <c r="L88" t="n">
+        <v>311.79</v>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4872,10 +5404,8 @@
           <t>秦文芳</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>15143988187</t>
-        </is>
+      <c r="B89" t="n">
+        <v>15143988187</v>
       </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
@@ -4916,6 +5446,14 @@
           <t>2024-04-19</t>
         </is>
       </c>
+      <c r="L89" t="n">
+        <v>453.96</v>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4923,10 +5461,8 @@
           <t>曹洋涛</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>13841309091</t>
-        </is>
+      <c r="B90" t="n">
+        <v>13841309091</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -4967,6 +5503,14 @@
           <t>2024-06-27</t>
         </is>
       </c>
+      <c r="L90" t="n">
+        <v>345.54</v>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4974,10 +5518,8 @@
           <t>朱华</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>13841231905</t>
-        </is>
+      <c r="B91" t="n">
+        <v>13841231905</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -5018,6 +5560,14 @@
           <t>2024-12-26</t>
         </is>
       </c>
+      <c r="L91" t="n">
+        <v>106.18</v>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5025,10 +5575,8 @@
           <t>秦敏丽</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>15253810979</t>
-        </is>
+      <c r="B92" t="n">
+        <v>15253810979</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -5073,6 +5621,14 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="L92" t="n">
+        <v>504.09</v>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5080,10 +5636,8 @@
           <t>陶静军</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>13796322517</t>
-        </is>
+      <c r="B93" t="n">
+        <v>13796322517</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -5124,6 +5678,14 @@
           <t>2024-02-25</t>
         </is>
       </c>
+      <c r="L93" t="n">
+        <v>549.5599999999999</v>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5131,10 +5693,8 @@
           <t>李芳</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>15986163070</t>
-        </is>
+      <c r="B94" t="n">
+        <v>15986163070</v>
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
@@ -5175,6 +5735,14 @@
           <t>2024-01-17</t>
         </is>
       </c>
+      <c r="L94" t="n">
+        <v>90.65000000000001</v>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5182,10 +5750,8 @@
           <t>吕文杰</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>13662195368</t>
-        </is>
+      <c r="B95" t="n">
+        <v>13662195368</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -5230,6 +5796,14 @@
           <t>2024-03-10</t>
         </is>
       </c>
+      <c r="L95" t="n">
+        <v>373.3</v>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5237,10 +5811,8 @@
           <t>吕华伟</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>13873971307</t>
-        </is>
+      <c r="B96" t="n">
+        <v>13873971307</v>
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
@@ -5277,6 +5849,14 @@
           <t>2024-08-29</t>
         </is>
       </c>
+      <c r="L96" t="n">
+        <v>756.54</v>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5284,10 +5864,8 @@
           <t>周平</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>15021045461</t>
-        </is>
+      <c r="B97" t="n">
+        <v>15021045461</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -5332,6 +5910,14 @@
           <t>2024-06-05</t>
         </is>
       </c>
+      <c r="L97" t="n">
+        <v>441.34</v>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5339,10 +5925,8 @@
           <t>杨娟</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>15034422521</t>
-        </is>
+      <c r="B98" t="n">
+        <v>15034422521</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -5383,6 +5967,14 @@
           <t>2024-12-06</t>
         </is>
       </c>
+      <c r="L98" t="n">
+        <v>316.04</v>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5390,10 +5982,8 @@
           <t>钱兰</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>13577269032</t>
-        </is>
+      <c r="B99" t="n">
+        <v>13577269032</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -5434,6 +6024,14 @@
           <t>2024-11-29</t>
         </is>
       </c>
+      <c r="L99" t="n">
+        <v>398.78</v>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5441,10 +6039,8 @@
           <t>魏霞英</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>18702455985</t>
-        </is>
+      <c r="B100" t="n">
+        <v>18702455985</v>
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
@@ -5481,6 +6077,14 @@
           <t>2024-02-16</t>
         </is>
       </c>
+      <c r="L100" t="n">
+        <v>432.89</v>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5488,10 +6092,8 @@
           <t>褚华</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>15949864786</t>
-        </is>
+      <c r="B101" t="n">
+        <v>15949864786</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -5532,6 +6134,14 @@
           <t>2024-09-26</t>
         </is>
       </c>
+      <c r="L101" t="n">
+        <v>390.37</v>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5539,10 +6149,8 @@
           <t>秦洋</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>13883781919</t>
-        </is>
+      <c r="B102" t="n">
+        <v>13883781919</v>
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
@@ -5579,6 +6187,14 @@
           <t>2024-10-19</t>
         </is>
       </c>
+      <c r="L102" t="n">
+        <v>75.05</v>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5586,10 +6202,8 @@
           <t>蒋杰英</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>18923534848</t>
-        </is>
+      <c r="B103" t="n">
+        <v>18923534848</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -5626,6 +6240,14 @@
           <t>2024-08-09</t>
         </is>
       </c>
+      <c r="L103" t="n">
+        <v>666.52</v>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5633,10 +6255,8 @@
           <t>卫静伟</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>15012372055</t>
-        </is>
+      <c r="B104" t="n">
+        <v>15012372055</v>
       </c>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
@@ -5673,6 +6293,14 @@
           <t>2024-07-11</t>
         </is>
       </c>
+      <c r="L104" t="n">
+        <v>686.5599999999999</v>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5680,10 +6308,8 @@
           <t>杨华</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>13567391900</t>
-        </is>
+      <c r="B105" t="n">
+        <v>13567391900</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -5720,6 +6346,14 @@
           <t>2024-01-12</t>
         </is>
       </c>
+      <c r="L105" t="n">
+        <v>710.99</v>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5727,10 +6361,8 @@
           <t>吴杰英</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>18923273798</t>
-        </is>
+      <c r="B106" t="n">
+        <v>18923273798</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -5771,6 +6403,14 @@
           <t>2024-02-12</t>
         </is>
       </c>
+      <c r="L106" t="n">
+        <v>631.8099999999999</v>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5778,10 +6418,8 @@
           <t>华明杰</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>15100099843</t>
-        </is>
+      <c r="B107" t="n">
+        <v>15100099843</v>
       </c>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
@@ -5822,6 +6460,14 @@
           <t>2024-02-13</t>
         </is>
       </c>
+      <c r="L107" t="n">
+        <v>669.25</v>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5829,10 +6475,8 @@
           <t>何娜秀</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>18954582942</t>
-        </is>
+      <c r="B108" t="n">
+        <v>18954582942</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -5873,6 +6517,14 @@
           <t>2024-05-22</t>
         </is>
       </c>
+      <c r="L108" t="n">
+        <v>326.15</v>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5880,10 +6532,8 @@
           <t>严娟</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>15869994494</t>
-        </is>
+      <c r="B109" t="n">
+        <v>15869994494</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -5924,6 +6574,14 @@
           <t>2024-01-09</t>
         </is>
       </c>
+      <c r="L109" t="n">
+        <v>77.65000000000001</v>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5931,10 +6589,8 @@
           <t>冯桂娜</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>13582238794</t>
-        </is>
+      <c r="B110" t="n">
+        <v>13582238794</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -5975,6 +6631,14 @@
           <t>2024-12-18</t>
         </is>
       </c>
+      <c r="L110" t="n">
+        <v>741.61</v>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5982,10 +6646,8 @@
           <t>何静</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>13653642357</t>
-        </is>
+      <c r="B111" t="n">
+        <v>13653642357</v>
       </c>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
@@ -6022,6 +6684,14 @@
           <t>2024-06-18</t>
         </is>
       </c>
+      <c r="L111" t="n">
+        <v>730.58</v>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6029,10 +6699,8 @@
           <t>郑秀</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>15912559046</t>
-        </is>
+      <c r="B112" t="n">
+        <v>15912559046</v>
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
@@ -6069,6 +6737,14 @@
           <t>2024-08-06</t>
         </is>
       </c>
+      <c r="L112" t="n">
+        <v>115.23</v>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -6076,10 +6752,8 @@
           <t>严伟</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>15083827101</t>
-        </is>
+      <c r="B113" t="n">
+        <v>15083827101</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -6124,6 +6798,14 @@
           <t>2024-03-05</t>
         </is>
       </c>
+      <c r="L113" t="n">
+        <v>591.34</v>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -6131,10 +6813,8 @@
           <t>钱平秀</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>13550766534</t>
-        </is>
+      <c r="B114" t="n">
+        <v>13550766534</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -6179,6 +6859,14 @@
           <t>2024-06-02</t>
         </is>
       </c>
+      <c r="L114" t="n">
+        <v>239.95</v>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6186,10 +6874,8 @@
           <t>孔伟</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>13953057347</t>
-        </is>
+      <c r="B115" t="n">
+        <v>13953057347</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -6234,6 +6920,14 @@
           <t>2024-03-24</t>
         </is>
       </c>
+      <c r="L115" t="n">
+        <v>793.67</v>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6241,10 +6935,8 @@
           <t>何文</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>18927267086</t>
-        </is>
+      <c r="B116" t="n">
+        <v>18927267086</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -6289,6 +6981,14 @@
           <t>2024-11-14</t>
         </is>
       </c>
+      <c r="L116" t="n">
+        <v>341.66</v>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6296,10 +6996,8 @@
           <t>金娟涛</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>18749477129</t>
-        </is>
+      <c r="B117" t="n">
+        <v>18749477129</v>
       </c>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
@@ -6336,6 +7034,14 @@
           <t>2024-06-04</t>
         </is>
       </c>
+      <c r="L117" t="n">
+        <v>396.04</v>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -6343,10 +7049,8 @@
           <t>陶洋静</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>15154340466</t>
-        </is>
+      <c r="B118" t="n">
+        <v>15154340466</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -6391,6 +7095,14 @@
           <t>2024-05-11</t>
         </is>
       </c>
+      <c r="L118" t="n">
+        <v>494.98</v>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -6398,10 +7110,8 @@
           <t>卫伟刚</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>13544111973</t>
-        </is>
+      <c r="B119" t="n">
+        <v>13544111973</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -6442,6 +7152,14 @@
           <t>2024-06-21</t>
         </is>
       </c>
+      <c r="L119" t="n">
+        <v>143.95</v>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -6449,10 +7167,8 @@
           <t>尤超超</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>13621884968</t>
-        </is>
+      <c r="B120" t="n">
+        <v>13621884968</v>
       </c>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
@@ -6489,6 +7205,14 @@
           <t>2024-02-21</t>
         </is>
       </c>
+      <c r="L120" t="n">
+        <v>464.27</v>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6496,10 +7220,8 @@
           <t>孙丽</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>13754341230</t>
-        </is>
+      <c r="B121" t="n">
+        <v>13754341230</v>
       </c>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
@@ -6536,6 +7258,14 @@
           <t>2024-09-11</t>
         </is>
       </c>
+      <c r="L121" t="n">
+        <v>659.24</v>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -6543,10 +7273,8 @@
           <t>陈敏平</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>13786003203</t>
-        </is>
+      <c r="B122" t="n">
+        <v>13786003203</v>
       </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
@@ -6587,6 +7315,14 @@
           <t>2024-01-17</t>
         </is>
       </c>
+      <c r="L122" t="n">
+        <v>411.63</v>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -6594,10 +7330,8 @@
           <t>赵强</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>18613171978</t>
-        </is>
+      <c r="B123" t="n">
+        <v>18613171978</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -6642,6 +7376,14 @@
           <t>2024-05-12</t>
         </is>
       </c>
+      <c r="L123" t="n">
+        <v>644.53</v>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -6649,10 +7391,8 @@
           <t>郑兰平</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>18685501137</t>
-        </is>
+      <c r="B124" t="n">
+        <v>18685501137</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -6693,6 +7433,14 @@
           <t>2024-01-02</t>
         </is>
       </c>
+      <c r="L124" t="n">
+        <v>95.88</v>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -6700,10 +7448,8 @@
           <t>陶静霞</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>13603716160</t>
-        </is>
+      <c r="B125" t="n">
+        <v>13603716160</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -6744,6 +7490,14 @@
           <t>2024-10-28</t>
         </is>
       </c>
+      <c r="L125" t="n">
+        <v>740.42</v>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -6751,10 +7505,8 @@
           <t>孔军</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>13618375307</t>
-        </is>
+      <c r="B126" t="n">
+        <v>13618375307</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -6795,6 +7547,14 @@
           <t>2024-10-08</t>
         </is>
       </c>
+      <c r="L126" t="n">
+        <v>120.8</v>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -6802,10 +7562,8 @@
           <t>张华</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>13780024432</t>
-        </is>
+      <c r="B127" t="n">
+        <v>13780024432</v>
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
@@ -6842,6 +7600,14 @@
           <t>2024-07-15</t>
         </is>
       </c>
+      <c r="L127" t="n">
+        <v>783.64</v>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -6849,10 +7615,8 @@
           <t>孔秀</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>18646706751</t>
-        </is>
+      <c r="B128" t="n">
+        <v>18646706751</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -6897,6 +7661,14 @@
           <t>2024-02-29</t>
         </is>
       </c>
+      <c r="L128" t="n">
+        <v>310.83</v>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -6904,10 +7676,8 @@
           <t>严洋杰</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>13907033508</t>
-        </is>
+      <c r="B129" t="n">
+        <v>13907033508</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -6952,6 +7722,14 @@
           <t>2024-05-27</t>
         </is>
       </c>
+      <c r="L129" t="n">
+        <v>313.94</v>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -6959,10 +7737,8 @@
           <t>尤超</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>13804169105</t>
-        </is>
+      <c r="B130" t="n">
+        <v>13804169105</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -7007,6 +7783,14 @@
           <t>2024-10-08</t>
         </is>
       </c>
+      <c r="L130" t="n">
+        <v>293.35</v>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -7014,10 +7798,8 @@
           <t>孔桂</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>13533953481</t>
-        </is>
+      <c r="B131" t="n">
+        <v>13533953481</v>
       </c>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
@@ -7058,6 +7840,14 @@
           <t>2024-09-08</t>
         </is>
       </c>
+      <c r="L131" t="n">
+        <v>428.46</v>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -7065,10 +7855,8 @@
           <t>华敏</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>15185512817</t>
-        </is>
+      <c r="B132" t="n">
+        <v>15185512817</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -7109,6 +7897,14 @@
           <t>2024-06-23</t>
         </is>
       </c>
+      <c r="L132" t="n">
+        <v>162.4</v>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -7116,10 +7912,8 @@
           <t>张军</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>13709723602</t>
-        </is>
+      <c r="B133" t="n">
+        <v>13709723602</v>
       </c>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
@@ -7160,6 +7954,14 @@
           <t>2024-08-27</t>
         </is>
       </c>
+      <c r="L133" t="n">
+        <v>759.86</v>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -7167,10 +7969,8 @@
           <t>陈芳</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>18610730871</t>
-        </is>
+      <c r="B134" t="n">
+        <v>18610730871</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -7211,6 +8011,14 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="L134" t="n">
+        <v>121.38</v>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -7218,10 +8026,8 @@
           <t>何洋超</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>13827414857</t>
-        </is>
+      <c r="B135" t="n">
+        <v>13827414857</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -7262,6 +8068,14 @@
           <t>2024-04-05</t>
         </is>
       </c>
+      <c r="L135" t="n">
+        <v>165.48</v>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -7269,10 +8083,8 @@
           <t>许芳</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>15942076327</t>
-        </is>
+      <c r="B136" t="n">
+        <v>15942076327</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -7313,6 +8125,14 @@
           <t>2024-12-20</t>
         </is>
       </c>
+      <c r="L136" t="n">
+        <v>456.03</v>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -7320,10 +8140,8 @@
           <t>冯艳强</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>18768790604</t>
-        </is>
+      <c r="B137" t="n">
+        <v>18768790604</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -7360,6 +8178,14 @@
           <t>2024-05-12</t>
         </is>
       </c>
+      <c r="L137" t="n">
+        <v>727.5</v>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -7367,10 +8193,8 @@
           <t>赵艳刚</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>18792739615</t>
-        </is>
+      <c r="B138" t="n">
+        <v>18792739615</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -7411,6 +8235,14 @@
           <t>2024-08-30</t>
         </is>
       </c>
+      <c r="L138" t="n">
+        <v>595.6799999999999</v>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -7418,10 +8250,8 @@
           <t>魏明艳</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>15226190384</t>
-        </is>
+      <c r="B139" t="n">
+        <v>15226190384</v>
       </c>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
@@ -7458,6 +8288,14 @@
           <t>2024-04-15</t>
         </is>
       </c>
+      <c r="L139" t="n">
+        <v>203.32</v>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -7465,10 +8303,8 @@
           <t>卫芳丽</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>18927111757</t>
-        </is>
+      <c r="B140" t="n">
+        <v>18927111757</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -7509,6 +8345,14 @@
           <t>2024-07-09</t>
         </is>
       </c>
+      <c r="L140" t="n">
+        <v>785.25</v>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -7516,10 +8360,8 @@
           <t>王洋</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>18769830521</t>
-        </is>
+      <c r="B141" t="n">
+        <v>18769830521</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -7560,6 +8402,14 @@
           <t>2024-01-08</t>
         </is>
       </c>
+      <c r="L141" t="n">
+        <v>361.31</v>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -7567,10 +8417,8 @@
           <t>郑军</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>15947106801</t>
-        </is>
+      <c r="B142" t="n">
+        <v>15947106801</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -7611,6 +8459,14 @@
           <t>2024-06-24</t>
         </is>
       </c>
+      <c r="L142" t="n">
+        <v>658.3099999999999</v>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -7618,10 +8474,8 @@
           <t>赵芳</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>15132672446</t>
-        </is>
+      <c r="B143" t="n">
+        <v>15132672446</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -7666,6 +8520,14 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="L143" t="n">
+        <v>539.23</v>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -7673,10 +8535,8 @@
           <t>韩兰</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>15954025998</t>
-        </is>
+      <c r="B144" t="n">
+        <v>15954025998</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -7717,6 +8577,14 @@
           <t>2024-02-14</t>
         </is>
       </c>
+      <c r="L144" t="n">
+        <v>602.11</v>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -7724,10 +8592,8 @@
           <t>褚兰</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>15935049602</t>
-        </is>
+      <c r="B145" t="n">
+        <v>15935049602</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -7772,6 +8638,14 @@
           <t>2024-06-04</t>
         </is>
       </c>
+      <c r="L145" t="n">
+        <v>561.36</v>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -7779,10 +8653,8 @@
           <t>施强军</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>18895070886</t>
-        </is>
+      <c r="B146" t="n">
+        <v>18895070886</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -7823,6 +8695,14 @@
           <t>2024-01-06</t>
         </is>
       </c>
+      <c r="L146" t="n">
+        <v>209.37</v>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -7830,10 +8710,8 @@
           <t>郑兰丽</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>18802215439</t>
-        </is>
+      <c r="B147" t="n">
+        <v>18802215439</v>
       </c>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
@@ -7874,6 +8752,14 @@
           <t>2024-04-08</t>
         </is>
       </c>
+      <c r="L147" t="n">
+        <v>253.77</v>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -7881,10 +8767,8 @@
           <t>杨强</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>15035102555</t>
-        </is>
+      <c r="B148" t="n">
+        <v>15035102555</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -7925,6 +8809,14 @@
           <t>2024-10-24</t>
         </is>
       </c>
+      <c r="L148" t="n">
+        <v>743.1900000000001</v>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -7932,10 +8824,8 @@
           <t>尤桂霞</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>15133243629</t>
-        </is>
+      <c r="B149" t="n">
+        <v>15133243629</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -7972,6 +8862,14 @@
           <t>2024-05-17</t>
         </is>
       </c>
+      <c r="L149" t="n">
+        <v>217.07</v>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -7979,10 +8877,8 @@
           <t>秦娜</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>18807596599</t>
-        </is>
+      <c r="B150" t="n">
+        <v>18807596599</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -8027,6 +8923,14 @@
           <t>2024-06-07</t>
         </is>
       </c>
+      <c r="L150" t="n">
+        <v>781.0700000000001</v>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -8034,10 +8938,8 @@
           <t>张军</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>13862941937</t>
-        </is>
+      <c r="B151" t="n">
+        <v>13862941937</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -8074,6 +8976,14 @@
           <t>2024-02-21</t>
         </is>
       </c>
+      <c r="L151" t="n">
+        <v>788.62</v>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -8081,10 +8991,8 @@
           <t>陶艳</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>15926475286</t>
-        </is>
+      <c r="B152" t="n">
+        <v>15926475286</v>
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
@@ -8125,6 +9033,14 @@
           <t>2024-01-14</t>
         </is>
       </c>
+      <c r="L152" t="n">
+        <v>782.55</v>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -8132,10 +9048,8 @@
           <t>赵兰刚</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>13584524032</t>
-        </is>
+      <c r="B153" t="n">
+        <v>13584524032</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -8176,6 +9090,14 @@
           <t>2024-04-17</t>
         </is>
       </c>
+      <c r="L153" t="n">
+        <v>588.75</v>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -8183,10 +9105,8 @@
           <t>冯敏敏</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>15230877972</t>
-        </is>
+      <c r="B154" t="n">
+        <v>15230877972</v>
       </c>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr"/>
@@ -8219,6 +9139,14 @@
           <t>2024-09-13</t>
         </is>
       </c>
+      <c r="L154" t="n">
+        <v>408.78</v>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -8226,10 +9154,8 @@
           <t>杨桂平</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>13658192048</t>
-        </is>
+      <c r="B155" t="n">
+        <v>13658192048</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -8274,6 +9200,14 @@
           <t>2024-10-28</t>
         </is>
       </c>
+      <c r="L155" t="n">
+        <v>59.87</v>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -8281,10 +9215,8 @@
           <t>华艳</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>13790257846</t>
-        </is>
+      <c r="B156" t="n">
+        <v>13790257846</v>
       </c>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr"/>
@@ -8321,6 +9253,14 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="L156" t="n">
+        <v>197.48</v>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -8328,10 +9268,8 @@
           <t>褚文</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>15972620846</t>
-        </is>
+      <c r="B157" t="n">
+        <v>15972620846</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -8372,6 +9310,14 @@
           <t>2024-02-11</t>
         </is>
       </c>
+      <c r="L157" t="n">
+        <v>543.28</v>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -8379,10 +9325,8 @@
           <t>曹丽丽</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>15050182562</t>
-        </is>
+      <c r="B158" t="n">
+        <v>15050182562</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -8423,6 +9367,14 @@
           <t>2024-02-16</t>
         </is>
       </c>
+      <c r="L158" t="n">
+        <v>494.46</v>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -8430,10 +9382,8 @@
           <t>褚华</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>15214992900</t>
-        </is>
+      <c r="B159" t="n">
+        <v>15214992900</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -8478,6 +9428,14 @@
           <t>2024-01-01</t>
         </is>
       </c>
+      <c r="L159" t="n">
+        <v>521.27</v>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -8485,10 +9443,8 @@
           <t>朱勇芳</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>18856321740</t>
-        </is>
+      <c r="B160" t="n">
+        <v>18856321740</v>
       </c>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
@@ -8525,6 +9481,14 @@
           <t>2024-04-12</t>
         </is>
       </c>
+      <c r="L160" t="n">
+        <v>417.4</v>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -8532,10 +9496,8 @@
           <t>卫静</t>
         </is>
       </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>13771193600</t>
-        </is>
+      <c r="B161" t="n">
+        <v>13771193600</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -8572,6 +9534,14 @@
           <t>2024-07-23</t>
         </is>
       </c>
+      <c r="L161" t="n">
+        <v>707.38</v>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -8579,10 +9549,8 @@
           <t>王刚芳</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>18662643850</t>
-        </is>
+      <c r="B162" t="n">
+        <v>18662643850</v>
       </c>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr">
@@ -8619,6 +9587,14 @@
           <t>2024-08-15</t>
         </is>
       </c>
+      <c r="L162" t="n">
+        <v>369.1</v>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -8626,10 +9602,8 @@
           <t>华刚</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>15113361094</t>
-        </is>
+      <c r="B163" t="n">
+        <v>15113361094</v>
       </c>
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr">
@@ -8666,6 +9640,14 @@
           <t>2024-05-21</t>
         </is>
       </c>
+      <c r="L163" t="n">
+        <v>699.91</v>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -8673,10 +9655,8 @@
           <t>尤敏强</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>18627768576</t>
-        </is>
+      <c r="B164" t="n">
+        <v>18627768576</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -8721,6 +9701,14 @@
           <t>2024-08-07</t>
         </is>
       </c>
+      <c r="L164" t="n">
+        <v>729.49</v>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -8728,10 +9716,8 @@
           <t>周明</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>15818870179</t>
-        </is>
+      <c r="B165" t="n">
+        <v>15818870179</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -8772,6 +9758,14 @@
           <t>2024-08-15</t>
         </is>
       </c>
+      <c r="L165" t="n">
+        <v>91.51000000000001</v>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -8779,10 +9773,8 @@
           <t>许军娜</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>13672345653</t>
-        </is>
+      <c r="B166" t="n">
+        <v>13672345653</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -8827,6 +9819,14 @@
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="L166" t="n">
+        <v>516.22</v>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -8834,10 +9834,8 @@
           <t>张英</t>
         </is>
       </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>13726890472</t>
-        </is>
+      <c r="B167" t="n">
+        <v>13726890472</v>
       </c>
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr">
@@ -8874,6 +9872,14 @@
           <t>2024-04-26</t>
         </is>
       </c>
+      <c r="L167" t="n">
+        <v>365.92</v>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -8881,10 +9887,8 @@
           <t>吕平明</t>
         </is>
       </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>13542164359</t>
-        </is>
+      <c r="B168" t="n">
+        <v>13542164359</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -8925,6 +9929,14 @@
           <t>2024-01-26</t>
         </is>
       </c>
+      <c r="L168" t="n">
+        <v>105.61</v>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -8932,10 +9944,8 @@
           <t>许明平</t>
         </is>
       </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>15914378844</t>
-        </is>
+      <c r="B169" t="n">
+        <v>15914378844</v>
       </c>
       <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr">
@@ -8976,6 +9986,14 @@
           <t>2024-06-28</t>
         </is>
       </c>
+      <c r="L169" t="n">
+        <v>600.8200000000001</v>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -8983,10 +10001,8 @@
           <t>严军涛</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>15063681541</t>
-        </is>
+      <c r="B170" t="n">
+        <v>15063681541</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -9027,6 +10043,14 @@
           <t>2024-10-22</t>
         </is>
       </c>
+      <c r="L170" t="n">
+        <v>162.53</v>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -9034,10 +10058,8 @@
           <t>王伟洋</t>
         </is>
       </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>15807860435</t>
-        </is>
+      <c r="B171" t="n">
+        <v>15807860435</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -9078,6 +10100,14 @@
           <t>2024-10-30</t>
         </is>
       </c>
+      <c r="L171" t="n">
+        <v>480.96</v>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -9085,10 +10115,8 @@
           <t>杨强</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>18673067182</t>
-        </is>
+      <c r="B172" t="n">
+        <v>18673067182</v>
       </c>
       <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr">
@@ -9125,6 +10153,14 @@
           <t>2024-11-10</t>
         </is>
       </c>
+      <c r="L172" t="n">
+        <v>267.77</v>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -9132,10 +10168,8 @@
           <t>钱文超</t>
         </is>
       </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>18986538590</t>
-        </is>
+      <c r="B173" t="n">
+        <v>18986538590</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -9172,6 +10206,14 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="L173" t="n">
+        <v>176.73</v>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -9179,10 +10221,8 @@
           <t>何伟平</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>15292217048</t>
-        </is>
+      <c r="B174" t="n">
+        <v>15292217048</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -9227,6 +10267,14 @@
           <t>2024-04-05</t>
         </is>
       </c>
+      <c r="L174" t="n">
+        <v>601.96</v>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -9234,10 +10282,8 @@
           <t>李文</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>13629073992</t>
-        </is>
+      <c r="B175" t="n">
+        <v>13629073992</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -9278,6 +10324,14 @@
           <t>2024-10-14</t>
         </is>
       </c>
+      <c r="L175" t="n">
+        <v>269.11</v>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -9285,10 +10339,8 @@
           <t>陈娟文</t>
         </is>
       </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>15137170864</t>
-        </is>
+      <c r="B176" t="n">
+        <v>15137170864</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -9325,6 +10377,14 @@
           <t>2024-05-01</t>
         </is>
       </c>
+      <c r="L176" t="n">
+        <v>156.14</v>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -9332,10 +10392,8 @@
           <t>何洋平</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>18801459967</t>
-        </is>
+      <c r="B177" t="n">
+        <v>18801459967</v>
       </c>
       <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr">
@@ -9372,6 +10430,14 @@
           <t>2024-07-07</t>
         </is>
       </c>
+      <c r="L177" t="n">
+        <v>97.11</v>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -9379,10 +10445,8 @@
           <t>朱霞军</t>
         </is>
       </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>15188430217</t>
-        </is>
+      <c r="B178" t="n">
+        <v>15188430217</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -9427,6 +10491,14 @@
           <t>2024-12-05</t>
         </is>
       </c>
+      <c r="L178" t="n">
+        <v>250.41</v>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -9434,10 +10506,8 @@
           <t>韩刚</t>
         </is>
       </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>18989016492</t>
-        </is>
+      <c r="B179" t="n">
+        <v>18989016492</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -9478,6 +10548,14 @@
           <t>2024-01-28</t>
         </is>
       </c>
+      <c r="L179" t="n">
+        <v>795.4400000000001</v>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -9485,10 +10563,8 @@
           <t>陈娟芳</t>
         </is>
       </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>18603088081</t>
-        </is>
+      <c r="B180" t="n">
+        <v>18603088081</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -9529,6 +10605,14 @@
           <t>2024-06-02</t>
         </is>
       </c>
+      <c r="L180" t="n">
+        <v>98.91</v>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -9536,10 +10620,8 @@
           <t>何文刚</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>13707288959</t>
-        </is>
+      <c r="B181" t="n">
+        <v>13707288959</v>
       </c>
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr"/>
@@ -9576,6 +10658,14 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="L181" t="n">
+        <v>145.59</v>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -9583,10 +10673,8 @@
           <t>王英杰</t>
         </is>
       </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>13712766208</t>
-        </is>
+      <c r="B182" t="n">
+        <v>13712766208</v>
       </c>
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr">
@@ -9623,6 +10711,14 @@
           <t>2024-03-30</t>
         </is>
       </c>
+      <c r="L182" t="n">
+        <v>658.64</v>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -9630,10 +10726,8 @@
           <t>严强军</t>
         </is>
       </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>15243596245</t>
-        </is>
+      <c r="B183" t="n">
+        <v>15243596245</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -9674,6 +10768,14 @@
           <t>2024-12-02</t>
         </is>
       </c>
+      <c r="L183" t="n">
+        <v>134.4</v>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -9681,10 +10783,8 @@
           <t>陈洋</t>
         </is>
       </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>15836909123</t>
-        </is>
+      <c r="B184" t="n">
+        <v>15836909123</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -9729,6 +10829,14 @@
           <t>2024-01-31</t>
         </is>
       </c>
+      <c r="L184" t="n">
+        <v>568.23</v>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -9736,10 +10844,8 @@
           <t>杨霞</t>
         </is>
       </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>13670243652</t>
-        </is>
+      <c r="B185" t="n">
+        <v>13670243652</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -9780,6 +10886,14 @@
           <t>2024-12-24</t>
         </is>
       </c>
+      <c r="L185" t="n">
+        <v>306.26</v>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -9787,10 +10901,8 @@
           <t>金华</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>15203648821</t>
-        </is>
+      <c r="B186" t="n">
+        <v>15203648821</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -9831,6 +10943,14 @@
           <t>2024-07-29</t>
         </is>
       </c>
+      <c r="L186" t="n">
+        <v>636.9</v>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -9838,10 +10958,8 @@
           <t>陈强磊</t>
         </is>
       </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>15906679986</t>
-        </is>
+      <c r="B187" t="n">
+        <v>15906679986</v>
       </c>
       <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr">
@@ -9878,6 +10996,14 @@
           <t>2024-03-30</t>
         </is>
       </c>
+      <c r="L187" t="n">
+        <v>675.61</v>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -9885,10 +11011,8 @@
           <t>冯英</t>
         </is>
       </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>15229862269</t>
-        </is>
+      <c r="B188" t="n">
+        <v>15229862269</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -9929,6 +11053,14 @@
           <t>2024-06-25</t>
         </is>
       </c>
+      <c r="L188" t="n">
+        <v>601.7</v>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -9936,10 +11068,8 @@
           <t>孔霞霞</t>
         </is>
       </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>18929983358</t>
-        </is>
+      <c r="B189" t="n">
+        <v>18929983358</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -9976,6 +11106,14 @@
           <t>2024-07-09</t>
         </is>
       </c>
+      <c r="L189" t="n">
+        <v>704.87</v>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -9983,10 +11121,8 @@
           <t>华伟</t>
         </is>
       </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>15148208493</t>
-        </is>
+      <c r="B190" t="n">
+        <v>15148208493</v>
       </c>
       <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr">
@@ -10027,6 +11163,14 @@
           <t>2024-01-16</t>
         </is>
       </c>
+      <c r="L190" t="n">
+        <v>728.45</v>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -10034,10 +11178,8 @@
           <t>赵娜</t>
         </is>
       </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>13876291430</t>
-        </is>
+      <c r="B191" t="n">
+        <v>13876291430</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -10074,6 +11216,14 @@
           <t>2024-10-21</t>
         </is>
       </c>
+      <c r="L191" t="n">
+        <v>248.72</v>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -10081,10 +11231,8 @@
           <t>姜勇</t>
         </is>
       </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>18987209986</t>
-        </is>
+      <c r="B192" t="n">
+        <v>18987209986</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -10125,6 +11273,14 @@
           <t>2024-11-13</t>
         </is>
       </c>
+      <c r="L192" t="n">
+        <v>66.12</v>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -10132,10 +11288,8 @@
           <t>陈芳磊</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>15830976691</t>
-        </is>
+      <c r="B193" t="n">
+        <v>15830976691</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -10172,6 +11326,14 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="L193" t="n">
+        <v>588.14</v>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -10179,10 +11341,8 @@
           <t>冯伟</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>18953079661</t>
-        </is>
+      <c r="B194" t="n">
+        <v>18953079661</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -10223,6 +11383,14 @@
           <t>2024-06-06</t>
         </is>
       </c>
+      <c r="L194" t="n">
+        <v>193.8</v>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -10230,10 +11398,8 @@
           <t>姜军</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>15053137956</t>
-        </is>
+      <c r="B195" t="n">
+        <v>15053137956</v>
       </c>
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr">
@@ -10270,6 +11436,14 @@
           <t>2024-06-28</t>
         </is>
       </c>
+      <c r="L195" t="n">
+        <v>137.48</v>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -10277,10 +11451,8 @@
           <t>李磊</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>13692025999</t>
-        </is>
+      <c r="B196" t="n">
+        <v>13692025999</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -10317,6 +11489,14 @@
           <t>2024-04-04</t>
         </is>
       </c>
+      <c r="L196" t="n">
+        <v>141.61</v>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -10324,10 +11504,8 @@
           <t>尤洋</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>18648904760</t>
-        </is>
+      <c r="B197" t="n">
+        <v>18648904760</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -10368,6 +11546,14 @@
           <t>2024-07-30</t>
         </is>
       </c>
+      <c r="L197" t="n">
+        <v>705.14</v>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -10375,10 +11561,8 @@
           <t>何娜霞</t>
         </is>
       </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>13970851732</t>
-        </is>
+      <c r="B198" t="n">
+        <v>13970851732</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -10419,6 +11603,14 @@
           <t>2024-02-07</t>
         </is>
       </c>
+      <c r="L198" t="n">
+        <v>690.26</v>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -10426,10 +11618,8 @@
           <t>施超</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>15881157449</t>
-        </is>
+      <c r="B199" t="n">
+        <v>15881157449</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -10470,6 +11660,14 @@
           <t>2024-05-25</t>
         </is>
       </c>
+      <c r="L199" t="n">
+        <v>55.55</v>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -10477,10 +11675,8 @@
           <t>赵兰</t>
         </is>
       </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>13704541840</t>
-        </is>
+      <c r="B200" t="n">
+        <v>13704541840</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -10517,6 +11713,14 @@
           <t>2024-10-28</t>
         </is>
       </c>
+      <c r="L200" t="n">
+        <v>393.75</v>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -10524,10 +11728,8 @@
           <t>孔杰文</t>
         </is>
       </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>13503858864</t>
-        </is>
+      <c r="B201" t="n">
+        <v>13503858864</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -10572,6 +11774,14 @@
           <t>2024-11-07</t>
         </is>
       </c>
+      <c r="L201" t="n">
+        <v>463.32</v>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -10579,10 +11789,8 @@
           <t>吕娜杰</t>
         </is>
       </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>15269333562</t>
-        </is>
+      <c r="B202" t="n">
+        <v>15269333562</v>
       </c>
       <c r="C202" t="inlineStr"/>
       <c r="D202" t="inlineStr">
@@ -10619,6 +11827,14 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="L202" t="n">
+        <v>435.36</v>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -10626,10 +11842,8 @@
           <t>孙超霞</t>
         </is>
       </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>18770920199</t>
-        </is>
+      <c r="B203" t="n">
+        <v>18770920199</v>
       </c>
       <c r="C203" t="inlineStr"/>
       <c r="D203" t="inlineStr"/>
@@ -10666,6 +11880,14 @@
           <t>2024-07-18</t>
         </is>
       </c>
+      <c r="L203" t="n">
+        <v>538.5</v>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -10673,10 +11895,8 @@
           <t>孔敏</t>
         </is>
       </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>18748580526</t>
-        </is>
+      <c r="B204" t="n">
+        <v>18748580526</v>
       </c>
       <c r="C204" t="inlineStr"/>
       <c r="D204" t="inlineStr"/>
@@ -10709,6 +11929,14 @@
           <t>2024-12-16</t>
         </is>
       </c>
+      <c r="L204" t="n">
+        <v>161.98</v>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -10716,10 +11944,8 @@
           <t>褚静</t>
         </is>
       </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>15197077454</t>
-        </is>
+      <c r="B205" t="n">
+        <v>15197077454</v>
       </c>
       <c r="C205" t="inlineStr"/>
       <c r="D205" t="inlineStr"/>
@@ -10756,6 +11982,14 @@
           <t>2024-05-28</t>
         </is>
       </c>
+      <c r="L205" t="n">
+        <v>525.0700000000001</v>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -10763,10 +11997,8 @@
           <t>孔英</t>
         </is>
       </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>18895394676</t>
-        </is>
+      <c r="B206" t="n">
+        <v>18895394676</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -10807,6 +12039,14 @@
           <t>2024-01-07</t>
         </is>
       </c>
+      <c r="L206" t="n">
+        <v>222.84</v>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -10814,10 +12054,8 @@
           <t>冯英</t>
         </is>
       </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>13584025787</t>
-        </is>
+      <c r="B207" t="n">
+        <v>13584025787</v>
       </c>
       <c r="C207" t="inlineStr"/>
       <c r="D207" t="inlineStr">
@@ -10854,6 +12092,14 @@
           <t>2024-01-22</t>
         </is>
       </c>
+      <c r="L207" t="n">
+        <v>52.29</v>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -10861,10 +12107,8 @@
           <t>曹杰</t>
         </is>
       </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>13705028164</t>
-        </is>
+      <c r="B208" t="n">
+        <v>13705028164</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -10901,6 +12145,14 @@
           <t>2024-03-25</t>
         </is>
       </c>
+      <c r="L208" t="n">
+        <v>503.59</v>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -10908,10 +12160,8 @@
           <t>李华平</t>
         </is>
       </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>13825209452</t>
-        </is>
+      <c r="B209" t="n">
+        <v>13825209452</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -10956,6 +12206,14 @@
           <t>2024-04-05</t>
         </is>
       </c>
+      <c r="L209" t="n">
+        <v>196.08</v>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -10963,10 +12221,8 @@
           <t>曹芳</t>
         </is>
       </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>13586027574</t>
-        </is>
+      <c r="B210" t="n">
+        <v>13586027574</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -11007,6 +12263,14 @@
           <t>2024-06-17</t>
         </is>
       </c>
+      <c r="L210" t="n">
+        <v>512.88</v>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -11014,10 +12278,8 @@
           <t>韩超</t>
         </is>
       </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>18708189655</t>
-        </is>
+      <c r="B211" t="n">
+        <v>18708189655</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -11058,6 +12320,14 @@
           <t>2024-11-01</t>
         </is>
       </c>
+      <c r="L211" t="n">
+        <v>735.74</v>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -11065,10 +12335,8 @@
           <t>张静</t>
         </is>
       </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>18870566036</t>
-        </is>
+      <c r="B212" t="n">
+        <v>18870566036</v>
       </c>
       <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr">
@@ -11105,6 +12373,14 @@
           <t>2024-05-31</t>
         </is>
       </c>
+      <c r="L212" t="n">
+        <v>628.16</v>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -11112,10 +12388,8 @@
           <t>金平</t>
         </is>
       </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>15960235158</t>
-        </is>
+      <c r="B213" t="n">
+        <v>15960235158</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -11156,6 +12430,14 @@
           <t>2024-02-18</t>
         </is>
       </c>
+      <c r="L213" t="n">
+        <v>405.11</v>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -11163,10 +12445,8 @@
           <t>何娟</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>18779052244</t>
-        </is>
+      <c r="B214" t="n">
+        <v>18779052244</v>
       </c>
       <c r="C214" t="inlineStr"/>
       <c r="D214" t="inlineStr">
@@ -11203,6 +12483,14 @@
           <t>2024-05-15</t>
         </is>
       </c>
+      <c r="L214" t="n">
+        <v>111.64</v>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -11210,10 +12498,8 @@
           <t>张强</t>
         </is>
       </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>13657905719</t>
-        </is>
+      <c r="B215" t="n">
+        <v>13657905719</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -11254,6 +12540,14 @@
           <t>2024-07-26</t>
         </is>
       </c>
+      <c r="L215" t="n">
+        <v>581.83</v>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -11261,10 +12555,8 @@
           <t>沈娟</t>
         </is>
       </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>13983359748</t>
-        </is>
+      <c r="B216" t="n">
+        <v>13983359748</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -11305,6 +12597,14 @@
           <t>2024-09-01</t>
         </is>
       </c>
+      <c r="L216" t="n">
+        <v>136.29</v>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -11312,10 +12612,8 @@
           <t>陶华秀</t>
         </is>
       </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>15230192209</t>
-        </is>
+      <c r="B217" t="n">
+        <v>15230192209</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -11360,6 +12658,14 @@
           <t>2024-03-09</t>
         </is>
       </c>
+      <c r="L217" t="n">
+        <v>356.29</v>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -11367,10 +12673,8 @@
           <t>沈兰杰</t>
         </is>
       </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>15240282532</t>
-        </is>
+      <c r="B218" t="n">
+        <v>15240282532</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -11415,6 +12719,14 @@
           <t>2024-05-01</t>
         </is>
       </c>
+      <c r="L218" t="n">
+        <v>332.91</v>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -11422,10 +12734,8 @@
           <t>褚磊勇</t>
         </is>
       </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>18920232091</t>
-        </is>
+      <c r="B219" t="n">
+        <v>18920232091</v>
       </c>
       <c r="C219" t="inlineStr"/>
       <c r="D219" t="inlineStr">
@@ -11462,6 +12772,14 @@
           <t>2024-09-21</t>
         </is>
       </c>
+      <c r="L219" t="n">
+        <v>334.67</v>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -11469,10 +12787,8 @@
           <t>秦洋</t>
         </is>
       </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>15271998290</t>
-        </is>
+      <c r="B220" t="n">
+        <v>15271998290</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -11513,6 +12829,14 @@
           <t>2024-01-30</t>
         </is>
       </c>
+      <c r="L220" t="n">
+        <v>245.56</v>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -11520,10 +12844,8 @@
           <t>金勇</t>
         </is>
       </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>13599138310</t>
-        </is>
+      <c r="B221" t="n">
+        <v>13599138310</v>
       </c>
       <c r="C221" t="inlineStr"/>
       <c r="D221" t="inlineStr">
@@ -11564,6 +12886,14 @@
           <t>2024-11-16</t>
         </is>
       </c>
+      <c r="L221" t="n">
+        <v>249.74</v>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -11571,10 +12901,8 @@
           <t>陈静</t>
         </is>
       </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>18673316806</t>
-        </is>
+      <c r="B222" t="n">
+        <v>18673316806</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -11619,6 +12947,14 @@
           <t>2024-01-27</t>
         </is>
       </c>
+      <c r="L222" t="n">
+        <v>64.41</v>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -11626,10 +12962,8 @@
           <t>杨杰勇</t>
         </is>
       </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>18852984241</t>
-        </is>
+      <c r="B223" t="n">
+        <v>18852984241</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -11674,6 +13008,14 @@
           <t>2024-11-27</t>
         </is>
       </c>
+      <c r="L223" t="n">
+        <v>239.93</v>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -11681,10 +13023,8 @@
           <t>华明艳</t>
         </is>
       </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>18726762590</t>
-        </is>
+      <c r="B224" t="n">
+        <v>18726762590</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -11729,6 +13069,14 @@
           <t>2024-12-05</t>
         </is>
       </c>
+      <c r="L224" t="n">
+        <v>784.51</v>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -11736,10 +13084,8 @@
           <t>施平华</t>
         </is>
       </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>15946149745</t>
-        </is>
+      <c r="B225" t="n">
+        <v>15946149745</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -11784,6 +13130,14 @@
           <t>2024-02-09</t>
         </is>
       </c>
+      <c r="L225" t="n">
+        <v>404.61</v>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -11791,10 +13145,8 @@
           <t>朱霞超</t>
         </is>
       </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>15909955049</t>
-        </is>
+      <c r="B226" t="n">
+        <v>15909955049</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -11839,6 +13191,14 @@
           <t>2024-04-23</t>
         </is>
       </c>
+      <c r="L226" t="n">
+        <v>282.45</v>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -11846,10 +13206,8 @@
           <t>朱杰</t>
         </is>
       </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>13928981159</t>
-        </is>
+      <c r="B227" t="n">
+        <v>13928981159</v>
       </c>
       <c r="C227" t="inlineStr"/>
       <c r="D227" t="inlineStr">
@@ -11886,6 +13244,14 @@
           <t>2024-08-18</t>
         </is>
       </c>
+      <c r="L227" t="n">
+        <v>672.23</v>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -11893,10 +13259,8 @@
           <t>华英丽</t>
         </is>
       </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>15039847422</t>
-        </is>
+      <c r="B228" t="n">
+        <v>15039847422</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -11937,6 +13301,14 @@
           <t>2024-08-18</t>
         </is>
       </c>
+      <c r="L228" t="n">
+        <v>793.3200000000001</v>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -11944,10 +13316,8 @@
           <t>陶芳</t>
         </is>
       </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>18741680613</t>
-        </is>
+      <c r="B229" t="n">
+        <v>18741680613</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -11984,6 +13354,14 @@
           <t>2024-12-13</t>
         </is>
       </c>
+      <c r="L229" t="n">
+        <v>752.8099999999999</v>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -11991,10 +13369,8 @@
           <t>何超</t>
         </is>
       </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>18694963830</t>
-        </is>
+      <c r="B230" t="n">
+        <v>18694963830</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -12035,6 +13411,14 @@
           <t>2024-01-31</t>
         </is>
       </c>
+      <c r="L230" t="n">
+        <v>475.98</v>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -12042,10 +13426,8 @@
           <t>陈娟</t>
         </is>
       </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>15920165557</t>
-        </is>
+      <c r="B231" t="n">
+        <v>15920165557</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -12090,6 +13472,14 @@
           <t>2024-09-09</t>
         </is>
       </c>
+      <c r="L231" t="n">
+        <v>422.37</v>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -12097,10 +13487,8 @@
           <t>施敏丽</t>
         </is>
       </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>15276400068</t>
-        </is>
+      <c r="B232" t="n">
+        <v>15276400068</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -12145,6 +13533,14 @@
           <t>2024-07-14</t>
         </is>
       </c>
+      <c r="L232" t="n">
+        <v>325.89</v>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -12152,10 +13548,8 @@
           <t>施军</t>
         </is>
       </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>15024441899</t>
-        </is>
+      <c r="B233" t="n">
+        <v>15024441899</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -12196,6 +13590,14 @@
           <t>2024-04-29</t>
         </is>
       </c>
+      <c r="L233" t="n">
+        <v>570.28</v>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -12203,10 +13605,8 @@
           <t>何明英</t>
         </is>
       </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>13970363094</t>
-        </is>
+      <c r="B234" t="n">
+        <v>13970363094</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -12251,6 +13651,14 @@
           <t>2024-06-19</t>
         </is>
       </c>
+      <c r="L234" t="n">
+        <v>335.62</v>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -12258,10 +13666,8 @@
           <t>李秀秀</t>
         </is>
       </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>15109413490</t>
-        </is>
+      <c r="B235" t="n">
+        <v>15109413490</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -12306,6 +13712,14 @@
           <t>2024-06-21</t>
         </is>
       </c>
+      <c r="L235" t="n">
+        <v>200.5</v>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -12313,10 +13727,8 @@
           <t>陈秀</t>
         </is>
       </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>15156948045</t>
-        </is>
+      <c r="B236" t="n">
+        <v>15156948045</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -12361,6 +13773,14 @@
           <t>2024-09-12</t>
         </is>
       </c>
+      <c r="L236" t="n">
+        <v>290.25</v>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -12368,10 +13788,8 @@
           <t>韩兰</t>
         </is>
       </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>13859802602</t>
-        </is>
+      <c r="B237" t="n">
+        <v>13859802602</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -12416,6 +13834,14 @@
           <t>2024-05-23</t>
         </is>
       </c>
+      <c r="L237" t="n">
+        <v>268.34</v>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -12423,10 +13849,8 @@
           <t>钱涛</t>
         </is>
       </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>15220319777</t>
-        </is>
+      <c r="B238" t="n">
+        <v>15220319777</v>
       </c>
       <c r="C238" t="inlineStr"/>
       <c r="D238" t="inlineStr">
@@ -12463,6 +13887,14 @@
           <t>2024-02-04</t>
         </is>
       </c>
+      <c r="L238" t="n">
+        <v>663.27</v>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -12470,10 +13902,8 @@
           <t>华英</t>
         </is>
       </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>18982308829</t>
-        </is>
+      <c r="B239" t="n">
+        <v>18982308829</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -12518,6 +13948,14 @@
           <t>2024-11-27</t>
         </is>
       </c>
+      <c r="L239" t="n">
+        <v>227.99</v>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -12525,10 +13963,8 @@
           <t>韩丽娟</t>
         </is>
       </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>13858694276</t>
-        </is>
+      <c r="B240" t="n">
+        <v>13858694276</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -12565,6 +14001,14 @@
           <t>2024-07-15</t>
         </is>
       </c>
+      <c r="L240" t="n">
+        <v>93.79000000000001</v>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -12572,10 +14016,8 @@
           <t>曹丽强</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>18915181788</t>
-        </is>
+      <c r="B241" t="n">
+        <v>18915181788</v>
       </c>
       <c r="C241" t="inlineStr"/>
       <c r="D241" t="inlineStr">
@@ -12616,6 +14058,14 @@
           <t>2024-10-30</t>
         </is>
       </c>
+      <c r="L241" t="n">
+        <v>219.95</v>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -12623,10 +14073,8 @@
           <t>钱娟磊</t>
         </is>
       </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>15072371798</t>
-        </is>
+      <c r="B242" t="n">
+        <v>15072371798</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -12667,6 +14115,14 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="L242" t="n">
+        <v>364.26</v>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -12674,10 +14130,8 @@
           <t>秦华平</t>
         </is>
       </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>18970847795</t>
-        </is>
+      <c r="B243" t="n">
+        <v>18970847795</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -12718,6 +14172,14 @@
           <t>2024-02-09</t>
         </is>
       </c>
+      <c r="L243" t="n">
+        <v>397.51</v>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -12725,10 +14187,8 @@
           <t>孙涛涛</t>
         </is>
       </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>18715915790</t>
-        </is>
+      <c r="B244" t="n">
+        <v>18715915790</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -12765,6 +14225,14 @@
           <t>2024-10-08</t>
         </is>
       </c>
+      <c r="L244" t="n">
+        <v>494.45</v>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -12772,10 +14240,8 @@
           <t>金娟</t>
         </is>
       </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>13820761239</t>
-        </is>
+      <c r="B245" t="n">
+        <v>13820761239</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -12820,6 +14286,14 @@
           <t>2024-11-27</t>
         </is>
       </c>
+      <c r="L245" t="n">
+        <v>73.45999999999999</v>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -12827,10 +14301,8 @@
           <t>孔平敏</t>
         </is>
       </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>18720706690</t>
-        </is>
+      <c r="B246" t="n">
+        <v>18720706690</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -12867,6 +14339,14 @@
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="L246" t="n">
+        <v>744.61</v>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -12874,10 +14354,8 @@
           <t>韩磊</t>
         </is>
       </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>13586497035</t>
-        </is>
+      <c r="B247" t="n">
+        <v>13586497035</v>
       </c>
       <c r="C247" t="inlineStr"/>
       <c r="D247" t="inlineStr">
@@ -12914,6 +14392,14 @@
           <t>2024-06-30</t>
         </is>
       </c>
+      <c r="L247" t="n">
+        <v>283.87</v>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -12921,10 +14407,8 @@
           <t>金伟涛</t>
         </is>
       </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>15112315550</t>
-        </is>
+      <c r="B248" t="n">
+        <v>15112315550</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -12965,6 +14449,14 @@
           <t>2024-12-11</t>
         </is>
       </c>
+      <c r="L248" t="n">
+        <v>648.13</v>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -12972,10 +14464,8 @@
           <t>韩超</t>
         </is>
       </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>13744045883</t>
-        </is>
+      <c r="B249" t="n">
+        <v>13744045883</v>
       </c>
       <c r="C249" t="inlineStr"/>
       <c r="D249" t="inlineStr">
@@ -13012,6 +14502,14 @@
           <t>2024-02-22</t>
         </is>
       </c>
+      <c r="L249" t="n">
+        <v>751.6</v>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -13019,10 +14517,8 @@
           <t>陈磊华</t>
         </is>
       </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>15803687156</t>
-        </is>
+      <c r="B250" t="n">
+        <v>15803687156</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -13063,6 +14559,14 @@
           <t>2024-03-13</t>
         </is>
       </c>
+      <c r="L250" t="n">
+        <v>732.8</v>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -13070,10 +14574,8 @@
           <t>韩平华</t>
         </is>
       </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>13645684467</t>
-        </is>
+      <c r="B251" t="n">
+        <v>13645684467</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
@@ -13118,6 +14620,14 @@
           <t>2024-04-21</t>
         </is>
       </c>
+      <c r="L251" t="n">
+        <v>719.66</v>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -13125,10 +14635,8 @@
           <t>冯霞</t>
         </is>
       </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>15178315975</t>
-        </is>
+      <c r="B252" t="n">
+        <v>15178315975</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
@@ -13169,6 +14677,14 @@
           <t>2024-04-16</t>
         </is>
       </c>
+      <c r="L252" t="n">
+        <v>662.85</v>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -13176,10 +14692,8 @@
           <t>孙静娜</t>
         </is>
       </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>15885423324</t>
-        </is>
+      <c r="B253" t="n">
+        <v>15885423324</v>
       </c>
       <c r="C253" t="inlineStr"/>
       <c r="D253" t="inlineStr"/>
@@ -13212,6 +14726,14 @@
           <t>2024-10-25</t>
         </is>
       </c>
+      <c r="L253" t="n">
+        <v>336.73</v>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -13219,10 +14741,8 @@
           <t>华华</t>
         </is>
       </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>18634467462</t>
-        </is>
+      <c r="B254" t="n">
+        <v>18634467462</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
@@ -13263,6 +14783,14 @@
           <t>2024-02-28</t>
         </is>
       </c>
+      <c r="L254" t="n">
+        <v>111.29</v>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -13270,10 +14798,8 @@
           <t>华娜</t>
         </is>
       </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>15802218169</t>
-        </is>
+      <c r="B255" t="n">
+        <v>15802218169</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
@@ -13314,6 +14840,14 @@
           <t>2024-07-16</t>
         </is>
       </c>
+      <c r="L255" t="n">
+        <v>660.25</v>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -13321,10 +14855,8 @@
           <t>李桂秀</t>
         </is>
       </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>15177402928</t>
-        </is>
+      <c r="B256" t="n">
+        <v>15177402928</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
@@ -13369,6 +14901,14 @@
           <t>2024-06-27</t>
         </is>
       </c>
+      <c r="L256" t="n">
+        <v>496.85</v>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -13376,10 +14916,8 @@
           <t>钱兰兰</t>
         </is>
       </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>15921836677</t>
-        </is>
+      <c r="B257" t="n">
+        <v>15921836677</v>
       </c>
       <c r="C257" t="inlineStr"/>
       <c r="D257" t="inlineStr"/>
@@ -13416,6 +14954,14 @@
           <t>2024-06-09</t>
         </is>
       </c>
+      <c r="L257" t="n">
+        <v>681.11</v>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -13423,10 +14969,8 @@
           <t>曹磊</t>
         </is>
       </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>13602223499</t>
-        </is>
+      <c r="B258" t="n">
+        <v>13602223499</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -13471,6 +15015,14 @@
           <t>2024-11-12</t>
         </is>
       </c>
+      <c r="L258" t="n">
+        <v>250.85</v>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -13478,10 +15030,8 @@
           <t>钱敏</t>
         </is>
       </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>18691524461</t>
-        </is>
+      <c r="B259" t="n">
+        <v>18691524461</v>
       </c>
       <c r="C259" t="inlineStr"/>
       <c r="D259" t="inlineStr">
@@ -13518,6 +15068,14 @@
           <t>2024-07-21</t>
         </is>
       </c>
+      <c r="L259" t="n">
+        <v>540.51</v>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -13525,10 +15083,8 @@
           <t>张娟静</t>
         </is>
       </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>13760186372</t>
-        </is>
+      <c r="B260" t="n">
+        <v>13760186372</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
@@ -13569,6 +15125,14 @@
           <t>2024-11-23</t>
         </is>
       </c>
+      <c r="L260" t="n">
+        <v>522.09</v>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -13576,10 +15140,8 @@
           <t>卫明杰</t>
         </is>
       </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>13741490038</t>
-        </is>
+      <c r="B261" t="n">
+        <v>13741490038</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -13620,6 +15182,14 @@
           <t>2024-12-15</t>
         </is>
       </c>
+      <c r="L261" t="n">
+        <v>77.97</v>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -13627,10 +15197,8 @@
           <t>朱秀</t>
         </is>
       </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>15028839047</t>
-        </is>
+      <c r="B262" t="n">
+        <v>15028839047</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -13671,6 +15239,14 @@
           <t>2024-05-29</t>
         </is>
       </c>
+      <c r="L262" t="n">
+        <v>126.14</v>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -13678,10 +15254,8 @@
           <t>蒋静</t>
         </is>
       </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>13949788795</t>
-        </is>
+      <c r="B263" t="n">
+        <v>13949788795</v>
       </c>
       <c r="C263" t="inlineStr"/>
       <c r="D263" t="inlineStr">
@@ -13718,6 +15292,14 @@
           <t>2024-09-10</t>
         </is>
       </c>
+      <c r="L263" t="n">
+        <v>325.82</v>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -13725,10 +15307,8 @@
           <t>华娟</t>
         </is>
       </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>15108580018</t>
-        </is>
+      <c r="B264" t="n">
+        <v>15108580018</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
@@ -13773,6 +15353,14 @@
           <t>2024-08-09</t>
         </is>
       </c>
+      <c r="L264" t="n">
+        <v>472.39</v>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -13780,10 +15368,8 @@
           <t>陶秀</t>
         </is>
       </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>18910781871</t>
-        </is>
+      <c r="B265" t="n">
+        <v>18910781871</v>
       </c>
       <c r="C265" t="inlineStr"/>
       <c r="D265" t="inlineStr"/>
@@ -13820,6 +15406,14 @@
           <t>2024-08-20</t>
         </is>
       </c>
+      <c r="L265" t="n">
+        <v>260.38</v>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -13827,10 +15421,8 @@
           <t>李娟平</t>
         </is>
       </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>13702693315</t>
-        </is>
+      <c r="B266" t="n">
+        <v>13702693315</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
@@ -13867,6 +15459,14 @@
           <t>2024-01-28</t>
         </is>
       </c>
+      <c r="L266" t="n">
+        <v>337.39</v>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -13874,10 +15474,8 @@
           <t>卫超</t>
         </is>
       </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>15850522411</t>
-        </is>
+      <c r="B267" t="n">
+        <v>15850522411</v>
       </c>
       <c r="C267" t="inlineStr"/>
       <c r="D267" t="inlineStr">
@@ -13914,6 +15512,14 @@
           <t>2024-02-08</t>
         </is>
       </c>
+      <c r="L267" t="n">
+        <v>536.12</v>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -13921,10 +15527,8 @@
           <t>朱勇兰</t>
         </is>
       </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>15001663382</t>
-        </is>
+      <c r="B268" t="n">
+        <v>15001663382</v>
       </c>
       <c r="C268" t="inlineStr"/>
       <c r="D268" t="inlineStr">
@@ -13961,6 +15565,14 @@
           <t>2024-03-07</t>
         </is>
       </c>
+      <c r="L268" t="n">
+        <v>109.32</v>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -13968,10 +15580,8 @@
           <t>卫刚</t>
         </is>
       </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>15862019011</t>
-        </is>
+      <c r="B269" t="n">
+        <v>15862019011</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
@@ -14012,6 +15622,14 @@
           <t>2024-03-30</t>
         </is>
       </c>
+      <c r="L269" t="n">
+        <v>530.6799999999999</v>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -14019,10 +15637,8 @@
           <t>张丽敏</t>
         </is>
       </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>13632394564</t>
-        </is>
+      <c r="B270" t="n">
+        <v>13632394564</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
@@ -14063,6 +15679,14 @@
           <t>2024-03-29</t>
         </is>
       </c>
+      <c r="L270" t="n">
+        <v>734.67</v>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -14070,10 +15694,8 @@
           <t>朱兰娟</t>
         </is>
       </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>15142095367</t>
-        </is>
+      <c r="B271" t="n">
+        <v>15142095367</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -14118,6 +15740,14 @@
           <t>2024-04-28</t>
         </is>
       </c>
+      <c r="L271" t="n">
+        <v>243.06</v>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -14125,10 +15755,8 @@
           <t>施杰娜</t>
         </is>
       </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>15826655914</t>
-        </is>
+      <c r="B272" t="n">
+        <v>15826655914</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -14173,6 +15801,14 @@
           <t>2024-02-23</t>
         </is>
       </c>
+      <c r="L272" t="n">
+        <v>372.37</v>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -14180,10 +15816,8 @@
           <t>秦明艳</t>
         </is>
       </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>15136952474</t>
-        </is>
+      <c r="B273" t="n">
+        <v>15136952474</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -14224,6 +15858,14 @@
           <t>2024-10-22</t>
         </is>
       </c>
+      <c r="L273" t="n">
+        <v>605.63</v>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -14231,10 +15873,8 @@
           <t>吕英</t>
         </is>
       </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>15236792415</t>
-        </is>
+      <c r="B274" t="n">
+        <v>15236792415</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -14279,6 +15919,14 @@
           <t>2024-12-03</t>
         </is>
       </c>
+      <c r="L274" t="n">
+        <v>511.44</v>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -14286,10 +15934,8 @@
           <t>尤娟超</t>
         </is>
       </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>13563906168</t>
-        </is>
+      <c r="B275" t="n">
+        <v>13563906168</v>
       </c>
       <c r="C275" t="inlineStr"/>
       <c r="D275" t="inlineStr"/>
@@ -14326,6 +15972,14 @@
           <t>2024-06-30</t>
         </is>
       </c>
+      <c r="L275" t="n">
+        <v>773.6799999999999</v>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -14333,10 +15987,8 @@
           <t>韩刚娜</t>
         </is>
       </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>13968371030</t>
-        </is>
+      <c r="B276" t="n">
+        <v>13968371030</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -14377,6 +16029,14 @@
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="L276" t="n">
+        <v>543.6</v>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -14384,10 +16044,8 @@
           <t>华明桂</t>
         </is>
       </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>13882649312</t>
-        </is>
+      <c r="B277" t="n">
+        <v>13882649312</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -14432,6 +16090,14 @@
           <t>2024-05-22</t>
         </is>
       </c>
+      <c r="L277" t="n">
+        <v>745.49</v>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -14439,10 +16105,8 @@
           <t>陈英平</t>
         </is>
       </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>15064563391</t>
-        </is>
+      <c r="B278" t="n">
+        <v>15064563391</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -14479,6 +16143,14 @@
           <t>2024-02-10</t>
         </is>
       </c>
+      <c r="L278" t="n">
+        <v>408.95</v>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -14486,10 +16158,8 @@
           <t>王丽桂</t>
         </is>
       </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>15949719670</t>
-        </is>
+      <c r="B279" t="n">
+        <v>15949719670</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -14530,6 +16200,14 @@
           <t>2024-02-25</t>
         </is>
       </c>
+      <c r="L279" t="n">
+        <v>585.14</v>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -14537,10 +16215,8 @@
           <t>褚艳兰</t>
         </is>
       </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>13816399490</t>
-        </is>
+      <c r="B280" t="n">
+        <v>13816399490</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -14581,6 +16257,14 @@
           <t>2024-08-02</t>
         </is>
       </c>
+      <c r="L280" t="n">
+        <v>523.03</v>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -14588,10 +16272,8 @@
           <t>陶刚刚</t>
         </is>
       </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>15281409841</t>
-        </is>
+      <c r="B281" t="n">
+        <v>15281409841</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -14636,6 +16318,14 @@
           <t>2024-02-23</t>
         </is>
       </c>
+      <c r="L281" t="n">
+        <v>365.8</v>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -14643,10 +16333,8 @@
           <t>何洋</t>
         </is>
       </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>13607963731</t>
-        </is>
+      <c r="B282" t="n">
+        <v>13607963731</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -14691,6 +16379,14 @@
           <t>2024-03-02</t>
         </is>
       </c>
+      <c r="L282" t="n">
+        <v>244.14</v>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -14698,10 +16394,8 @@
           <t>吴艳涛</t>
         </is>
       </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>13984523542</t>
-        </is>
+      <c r="B283" t="n">
+        <v>13984523542</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
@@ -14742,6 +16436,14 @@
           <t>2024-04-09</t>
         </is>
       </c>
+      <c r="L283" t="n">
+        <v>550.89</v>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -14749,10 +16451,8 @@
           <t>褚平刚</t>
         </is>
       </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>13886523777</t>
-        </is>
+      <c r="B284" t="n">
+        <v>13886523777</v>
       </c>
       <c r="C284" t="inlineStr"/>
       <c r="D284" t="inlineStr">
@@ -14793,6 +16493,14 @@
           <t>2024-02-27</t>
         </is>
       </c>
+      <c r="L284" t="n">
+        <v>65.05</v>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -14800,10 +16508,8 @@
           <t>秦芳芳</t>
         </is>
       </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>13652781055</t>
-        </is>
+      <c r="B285" t="n">
+        <v>13652781055</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
@@ -14848,6 +16554,14 @@
           <t>2024-04-05</t>
         </is>
       </c>
+      <c r="L285" t="n">
+        <v>354.58</v>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -14855,10 +16569,8 @@
           <t>何涛强</t>
         </is>
       </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>13960943913</t>
-        </is>
+      <c r="B286" t="n">
+        <v>13960943913</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
@@ -14895,6 +16607,14 @@
           <t>2024-04-11</t>
         </is>
       </c>
+      <c r="L286" t="n">
+        <v>575.51</v>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -14902,10 +16622,8 @@
           <t>孔霞</t>
         </is>
       </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>13528620929</t>
-        </is>
+      <c r="B287" t="n">
+        <v>13528620929</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
@@ -14946,6 +16664,14 @@
           <t>2024-12-15</t>
         </is>
       </c>
+      <c r="L287" t="n">
+        <v>297.44</v>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -14953,10 +16679,8 @@
           <t>沈磊</t>
         </is>
       </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>15073938992</t>
-        </is>
+      <c r="B288" t="n">
+        <v>15073938992</v>
       </c>
       <c r="C288" t="inlineStr"/>
       <c r="D288" t="inlineStr">
@@ -14997,6 +16721,14 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="L288" t="n">
+        <v>510.08</v>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -15004,10 +16736,8 @@
           <t>华娜芳</t>
         </is>
       </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>18661087082</t>
-        </is>
+      <c r="B289" t="n">
+        <v>18661087082</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
@@ -15052,6 +16782,14 @@
           <t>2024-09-08</t>
         </is>
       </c>
+      <c r="L289" t="n">
+        <v>651.03</v>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -15059,10 +16797,8 @@
           <t>王静</t>
         </is>
       </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>15883882176</t>
-        </is>
+      <c r="B290" t="n">
+        <v>15883882176</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
@@ -15103,6 +16839,14 @@
           <t>2024-03-08</t>
         </is>
       </c>
+      <c r="L290" t="n">
+        <v>360.69</v>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -15110,10 +16854,8 @@
           <t>陈强强</t>
         </is>
       </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>13522280194</t>
-        </is>
+      <c r="B291" t="n">
+        <v>13522280194</v>
       </c>
       <c r="C291" t="inlineStr"/>
       <c r="D291" t="inlineStr">
@@ -15154,6 +16896,14 @@
           <t>2024-06-30</t>
         </is>
       </c>
+      <c r="L291" t="n">
+        <v>709.36</v>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -15161,10 +16911,8 @@
           <t>曹芳</t>
         </is>
       </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>13795350637</t>
-        </is>
+      <c r="B292" t="n">
+        <v>13795350637</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
@@ -15205,6 +16953,14 @@
           <t>2024-04-30</t>
         </is>
       </c>
+      <c r="L292" t="n">
+        <v>733.29</v>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -15212,10 +16968,8 @@
           <t>赵明磊</t>
         </is>
       </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>13784185201</t>
-        </is>
+      <c r="B293" t="n">
+        <v>13784185201</v>
       </c>
       <c r="C293" t="inlineStr"/>
       <c r="D293" t="inlineStr">
@@ -15252,6 +17006,14 @@
           <t>2024-04-27</t>
         </is>
       </c>
+      <c r="L293" t="n">
+        <v>253.14</v>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -15259,10 +17021,8 @@
           <t>陶刚</t>
         </is>
       </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>13954705549</t>
-        </is>
+      <c r="B294" t="n">
+        <v>13954705549</v>
       </c>
       <c r="C294" t="inlineStr"/>
       <c r="D294" t="inlineStr">
@@ -15299,6 +17059,14 @@
           <t>2024-10-16</t>
         </is>
       </c>
+      <c r="L294" t="n">
+        <v>215.37</v>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -15306,10 +17074,8 @@
           <t>吕勇</t>
         </is>
       </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>13891969395</t>
-        </is>
+      <c r="B295" t="n">
+        <v>13891969395</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
@@ -15350,6 +17116,14 @@
           <t>2024-03-27</t>
         </is>
       </c>
+      <c r="L295" t="n">
+        <v>119.67</v>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -15357,10 +17131,8 @@
           <t>华丽娜</t>
         </is>
       </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>18871212413</t>
-        </is>
+      <c r="B296" t="n">
+        <v>18871212413</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
@@ -15401,6 +17173,14 @@
           <t>2024-09-24</t>
         </is>
       </c>
+      <c r="L296" t="n">
+        <v>363.64</v>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -15408,10 +17188,8 @@
           <t>陶强</t>
         </is>
       </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>15977319227</t>
-        </is>
+      <c r="B297" t="n">
+        <v>15977319227</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
@@ -15456,6 +17234,14 @@
           <t>2024-08-03</t>
         </is>
       </c>
+      <c r="L297" t="n">
+        <v>777.62</v>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>618大促</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -15463,10 +17249,8 @@
           <t>施磊强</t>
         </is>
       </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>18994319165</t>
-        </is>
+      <c r="B298" t="n">
+        <v>18994319165</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
@@ -15503,6 +17287,14 @@
           <t>2024-03-02</t>
         </is>
       </c>
+      <c r="L298" t="n">
+        <v>786.75</v>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>夏日焕肤</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -15510,10 +17302,8 @@
           <t>周艳文</t>
         </is>
       </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>15876449747</t>
-        </is>
+      <c r="B299" t="n">
+        <v>15876449747</v>
       </c>
       <c r="C299" t="inlineStr"/>
       <c r="D299" t="inlineStr">
@@ -15550,6 +17340,14 @@
           <t>2024-06-07</t>
         </is>
       </c>
+      <c r="L299" t="n">
+        <v>98.52</v>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -15557,10 +17355,8 @@
           <t>华明</t>
         </is>
       </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>18879741636</t>
-        </is>
+      <c r="B300" t="n">
+        <v>18879741636</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
@@ -15605,6 +17401,14 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="L300" t="n">
+        <v>564.27</v>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>新店开业</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -15612,10 +17416,8 @@
           <t>韩明</t>
         </is>
       </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>18864969277</t>
-        </is>
+      <c r="B301" t="n">
+        <v>18864969277</v>
       </c>
       <c r="C301" t="inlineStr"/>
       <c r="D301" t="inlineStr"/>
@@ -15648,6 +17450,14 @@
           <t>2024-01-26</t>
         </is>
       </c>
+      <c r="L301" t="n">
+        <v>223.57</v>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>常规投放</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
